--- a/GP2/Versuch_E12/Messwerte_E12.xlsx
+++ b/GP2/Versuch_E12/Messwerte_E12.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fynnlucca/Documents/Grundpraktikum-1/GP2/Versuch_E12/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A498376-4555-5D4E-9780-414B1A2D21A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5498148-BE65-0647-8F9D-679DFBDF1D5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{C0443A9E-E164-B441-9430-21559BD42383}"/>
+    <workbookView xWindow="14040" yWindow="2780" windowWidth="28040" windowHeight="17180" xr2:uid="{C0443A9E-E164-B441-9430-21559BD42383}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,12 +36,42 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Versuch E12</t>
   </si>
   <si>
     <t>Aufgabe 1</t>
+  </si>
+  <si>
+    <t>Messung</t>
+  </si>
+  <si>
+    <t>Freq [Hz]</t>
+  </si>
+  <si>
+    <t>U_0 [V]</t>
+  </si>
+  <si>
+    <t>U_R [V]</t>
+  </si>
+  <si>
+    <t>R = 1kOhm</t>
+  </si>
+  <si>
+    <t>theta [°]</t>
+  </si>
+  <si>
+    <t>Einstellungen:</t>
+  </si>
+  <si>
+    <t>Wechselstrom 1V</t>
+  </si>
+  <si>
+    <t>Theta B-&gt; A</t>
+  </si>
+  <si>
+    <t>Bei den hohen Werten +-5°</t>
   </si>
 </sst>
 </file>
@@ -413,17 +443,451 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5060539-FDFE-EB46-A872-C3D23F847888}">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>100</v>
+      </c>
+      <c r="B11">
+        <v>1.97</v>
+      </c>
+      <c r="C11">
+        <v>1.9239999999999999</v>
+      </c>
+      <c r="D11">
+        <v>8.1110000000000007</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>200</v>
+      </c>
+      <c r="B12">
+        <v>1.899</v>
+      </c>
+      <c r="C12">
+        <v>1.7989999999999999</v>
+      </c>
+      <c r="D12">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>300</v>
+      </c>
+      <c r="B13">
+        <v>1.794</v>
+      </c>
+      <c r="C13">
+        <v>1.63</v>
+      </c>
+      <c r="D13">
+        <v>21.97</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>400</v>
+      </c>
+      <c r="B14">
+        <v>1.706</v>
+      </c>
+      <c r="C14">
+        <v>1.478</v>
+      </c>
+      <c r="D14">
+        <v>26.54</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>500</v>
+      </c>
+      <c r="B15">
+        <v>1.635</v>
+      </c>
+      <c r="C15">
+        <v>1.3180000000000001</v>
+      </c>
+      <c r="D15">
+        <v>31.95</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>600</v>
+      </c>
+      <c r="B16">
+        <v>1.5649999999999999</v>
+      </c>
+      <c r="C16">
+        <v>1.1930000000000001</v>
+      </c>
+      <c r="D16">
+        <v>36.9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>700</v>
+      </c>
+      <c r="B17">
+        <v>1.53</v>
+      </c>
+      <c r="C17">
+        <v>1.0780000000000001</v>
+      </c>
+      <c r="D17">
+        <v>40.520000000000003</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>800</v>
+      </c>
+      <c r="B18">
+        <v>1.4770000000000001</v>
+      </c>
+      <c r="C18">
+        <v>0.98850000000000005</v>
+      </c>
+      <c r="D18">
+        <v>46.42</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>900</v>
+      </c>
+      <c r="B19">
+        <v>1.4419999999999999</v>
+      </c>
+      <c r="C19">
+        <v>0.98839999999999995</v>
+      </c>
+      <c r="D19">
+        <v>49.76</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>1000</v>
+      </c>
+      <c r="B20">
+        <v>1.4239999999999999</v>
+      </c>
+      <c r="C20">
+        <v>0.83709999999999996</v>
+      </c>
+      <c r="D20">
+        <v>50.84</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>2000</v>
+      </c>
+      <c r="B21">
+        <v>1.319</v>
+      </c>
+      <c r="C21">
+        <v>0.46310000000000001</v>
+      </c>
+      <c r="D21">
+        <v>68.010000000000005</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>3000</v>
+      </c>
+      <c r="B22">
+        <v>1.284</v>
+      </c>
+      <c r="C22">
+        <v>0.3206</v>
+      </c>
+      <c r="D22">
+        <v>75.540000000000006</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>4000</v>
+      </c>
+      <c r="B23">
+        <v>1.246</v>
+      </c>
+      <c r="C23">
+        <v>0.24060000000000001</v>
+      </c>
+      <c r="D23">
+        <v>77.290000000000006</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>5000</v>
+      </c>
+      <c r="B24">
+        <v>1.246</v>
+      </c>
+      <c r="C24">
+        <v>0.19420000000000001</v>
+      </c>
+      <c r="D24">
+        <v>79.92</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>6000</v>
+      </c>
+      <c r="B25">
+        <v>1.246</v>
+      </c>
+      <c r="C25">
+        <v>0.16220000000000001</v>
+      </c>
+      <c r="D25">
+        <v>79.63</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>7000</v>
+      </c>
+      <c r="B26">
+        <v>1.2370000000000001</v>
+      </c>
+      <c r="C26">
+        <v>0.1416</v>
+      </c>
+      <c r="D26">
+        <v>80.25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>8000</v>
+      </c>
+      <c r="B27">
+        <v>1.2370000000000001</v>
+      </c>
+      <c r="C27">
+        <v>0.1255</v>
+      </c>
+      <c r="D27">
+        <v>81.16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>9000</v>
+      </c>
+      <c r="B28">
+        <v>1.2370000000000001</v>
+      </c>
+      <c r="C28">
+        <v>0.11020000000000001</v>
+      </c>
+      <c r="D28">
+        <v>82.03</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>10000</v>
+      </c>
+      <c r="B29">
+        <v>1.2370000000000001</v>
+      </c>
+      <c r="C29">
+        <v>9.9479999999999999E-2</v>
+      </c>
+      <c r="D29">
+        <v>82.66</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>20000</v>
+      </c>
+      <c r="B30">
+        <v>1.2370000000000001</v>
+      </c>
+      <c r="C30">
+        <v>5.1159999999999997E-2</v>
+      </c>
+      <c r="D30">
+        <v>82.9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>30000</v>
+      </c>
+      <c r="B31">
+        <v>1.228</v>
+      </c>
+      <c r="C31">
+        <v>3.5450000000000002E-2</v>
+      </c>
+      <c r="D31">
+        <v>82.92</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>40000</v>
+      </c>
+      <c r="B32">
+        <v>1.228</v>
+      </c>
+      <c r="C32">
+        <v>2.7369999999999998E-2</v>
+      </c>
+      <c r="D32">
+        <v>83.83</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>50000</v>
+      </c>
+      <c r="B33">
+        <v>1.228</v>
+      </c>
+      <c r="C33">
+        <v>2.2440000000000002E-2</v>
+      </c>
+      <c r="D33">
+        <v>84.06</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>60000</v>
+      </c>
+      <c r="B34">
+        <v>1.21</v>
+      </c>
+      <c r="C34">
+        <v>1.8849999999999999E-2</v>
+      </c>
+      <c r="D34">
+        <v>82.44</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <v>70000</v>
+      </c>
+      <c r="B35">
+        <v>1.202</v>
+      </c>
+      <c r="C35">
+        <v>1.6150000000000001E-2</v>
+      </c>
+      <c r="D35">
+        <v>81.209999999999994</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <v>80000</v>
+      </c>
+      <c r="B36">
+        <v>1.1930000000000001</v>
+      </c>
+      <c r="C36">
+        <v>1.5259999999999999E-2</v>
+      </c>
+      <c r="D36">
+        <v>85.97</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <v>90000</v>
+      </c>
+      <c r="B37">
+        <v>1.175</v>
+      </c>
+      <c r="C37">
+        <v>1.256E-2</v>
+      </c>
+      <c r="D37">
+        <v>81.64</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>100000</v>
+      </c>
+      <c r="B38">
+        <v>1.149</v>
+      </c>
+      <c r="C38">
+        <v>1.077E-2</v>
+      </c>
+      <c r="D38">
+        <v>82.72</v>
       </c>
     </row>
   </sheetData>

--- a/GP2/Versuch_E12/Messwerte_E12.xlsx
+++ b/GP2/Versuch_E12/Messwerte_E12.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fynnlucca/Documents/Grundpraktikum-1/GP2/Versuch_E12/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5498148-BE65-0647-8F9D-679DFBDF1D5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA29BF65-4A2D-B546-96D5-0C30F132DDDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14040" yWindow="2780" windowWidth="28040" windowHeight="17180" xr2:uid="{C0443A9E-E164-B441-9430-21559BD42383}"/>
+    <workbookView xWindow="20000" yWindow="3280" windowWidth="28040" windowHeight="17180" xr2:uid="{C0443A9E-E164-B441-9430-21559BD42383}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="15">
   <si>
     <t>Versuch E12</t>
   </si>
@@ -72,6 +72,15 @@
   </si>
   <si>
     <t>Bei den hohen Werten +-5°</t>
+  </si>
+  <si>
+    <t>Messung mit Tiefpassfilter</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>A</t>
   </si>
 </sst>
 </file>
@@ -443,7 +452,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5060539-FDFE-EB46-A872-C3D23F847888}">
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D104"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
@@ -485,412 +494,874 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
+      <c r="B10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
         <v>3</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B11" t="s">
         <v>4</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C11" t="s">
         <v>5</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D11" t="s">
         <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11">
-        <v>100</v>
-      </c>
-      <c r="B11">
-        <v>1.97</v>
-      </c>
-      <c r="C11">
-        <v>1.9239999999999999</v>
-      </c>
-      <c r="D11">
-        <v>8.1110000000000007</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12">
-        <v>200</v>
+        <v>10</v>
       </c>
       <c r="B12">
-        <v>1.899</v>
+        <v>1.97</v>
       </c>
       <c r="C12">
-        <v>1.7989999999999999</v>
+        <v>3.5900000000000001E-2</v>
       </c>
       <c r="D12">
-        <v>15.4</v>
+        <v>84.43</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13">
-        <v>300</v>
+        <v>20</v>
       </c>
       <c r="B13">
-        <v>1.794</v>
+        <v>1.9870000000000001</v>
       </c>
       <c r="C13">
-        <v>1.63</v>
+        <v>6.4619999999999997E-2</v>
       </c>
       <c r="D13">
-        <v>21.97</v>
+        <v>88.23</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14">
-        <v>400</v>
+        <v>30</v>
       </c>
       <c r="B14">
-        <v>1.706</v>
+        <v>1.9870000000000001</v>
       </c>
       <c r="C14">
-        <v>1.478</v>
+        <v>9.2899999999999996E-2</v>
       </c>
       <c r="D14">
-        <v>26.54</v>
+        <v>276.5</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15">
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="B15">
-        <v>1.635</v>
+        <v>10.987</v>
       </c>
       <c r="C15">
-        <v>1.3180000000000001</v>
+        <v>0.121</v>
       </c>
       <c r="D15">
-        <v>31.95</v>
+        <v>275.3</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16">
-        <v>600</v>
+        <v>50</v>
       </c>
       <c r="B16">
-        <v>1.5649999999999999</v>
+        <v>1.9870000000000001</v>
       </c>
       <c r="C16">
-        <v>1.1930000000000001</v>
+        <v>0.1479</v>
       </c>
       <c r="D16">
-        <v>36.9</v>
+        <v>276.5</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17">
-        <v>700</v>
+        <v>60</v>
       </c>
       <c r="B17">
-        <v>1.53</v>
+        <v>1.9870000000000001</v>
       </c>
       <c r="C17">
-        <v>1.0780000000000001</v>
+        <v>0.1757</v>
       </c>
       <c r="D17">
-        <v>40.520000000000003</v>
+        <v>276.3</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18">
-        <v>800</v>
+        <v>70</v>
       </c>
       <c r="B18">
-        <v>1.4770000000000001</v>
+        <v>1.97</v>
       </c>
       <c r="C18">
-        <v>0.98850000000000005</v>
+        <v>0.20319999999999999</v>
       </c>
       <c r="D18">
-        <v>46.42</v>
+        <v>278.8</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19">
-        <v>900</v>
+        <v>80</v>
       </c>
       <c r="B19">
-        <v>1.4419999999999999</v>
+        <v>1.97</v>
       </c>
       <c r="C19">
-        <v>0.98839999999999995</v>
+        <v>0.2281</v>
       </c>
       <c r="D19">
-        <v>49.76</v>
+        <v>278.8</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="B20">
-        <v>1.4239999999999999</v>
+        <v>1.97</v>
       </c>
       <c r="C20">
-        <v>0.83709999999999996</v>
+        <v>0.25480000000000003</v>
       </c>
       <c r="D20">
-        <v>50.84</v>
+        <v>280.39999999999998</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21">
-        <v>2000</v>
+        <v>100</v>
       </c>
       <c r="B21">
-        <v>1.319</v>
+        <v>1.97</v>
       </c>
       <c r="C21">
-        <v>0.46310000000000001</v>
+        <v>0.28160000000000002</v>
       </c>
       <c r="D21">
-        <v>68.010000000000005</v>
+        <v>281.10000000000002</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22">
-        <v>3000</v>
+        <v>200</v>
       </c>
       <c r="B22">
-        <v>1.284</v>
+        <v>1.877</v>
       </c>
       <c r="C22">
-        <v>0.3206</v>
+        <v>0.50770000000000004</v>
       </c>
       <c r="D22">
-        <v>75.540000000000006</v>
+        <v>288.5</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23">
-        <v>4000</v>
+        <v>300</v>
       </c>
       <c r="B23">
-        <v>1.246</v>
+        <v>1.7809999999999999</v>
       </c>
       <c r="C23">
-        <v>0.24060000000000001</v>
+        <v>0.68579999999999997</v>
       </c>
       <c r="D23">
-        <v>77.290000000000006</v>
+        <v>294.7</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24">
-        <v>5000</v>
+        <v>400</v>
       </c>
       <c r="B24">
-        <v>1.246</v>
+        <v>1.6930000000000001</v>
       </c>
       <c r="C24">
-        <v>0.19420000000000001</v>
+        <v>0.81489999999999996</v>
       </c>
       <c r="D24">
-        <v>79.92</v>
+        <v>300.8</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25">
-        <v>6000</v>
+        <v>500</v>
       </c>
       <c r="B25">
-        <v>1.246</v>
+        <v>1.623</v>
       </c>
       <c r="C25">
-        <v>0.16220000000000001</v>
+        <v>0.90849999999999997</v>
       </c>
       <c r="D25">
-        <v>79.63</v>
+        <v>305.89999999999998</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26">
-        <v>7000</v>
+        <v>600</v>
       </c>
       <c r="B26">
-        <v>1.2370000000000001</v>
+        <v>1.5609999999999999</v>
       </c>
       <c r="C26">
-        <v>0.1416</v>
+        <v>0.97960000000000003</v>
       </c>
       <c r="D26">
-        <v>80.25</v>
+        <v>311.7</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27">
-        <v>8000</v>
+        <v>700</v>
       </c>
       <c r="B27">
-        <v>1.2370000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="C27">
-        <v>0.1255</v>
+        <v>1.024</v>
       </c>
       <c r="D27">
-        <v>81.16</v>
+        <v>315.3</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28">
-        <v>9000</v>
+        <v>800</v>
       </c>
       <c r="B28">
-        <v>1.2370000000000001</v>
+        <v>1.4650000000000001</v>
       </c>
       <c r="C28">
-        <v>0.11020000000000001</v>
+        <v>1.069</v>
       </c>
       <c r="D28">
-        <v>82.03</v>
+        <v>318.8</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29">
-        <v>10000</v>
+        <v>900</v>
       </c>
       <c r="B29">
-        <v>1.2370000000000001</v>
+        <v>1.43</v>
       </c>
       <c r="C29">
-        <v>9.9479999999999999E-2</v>
+        <v>1.095</v>
       </c>
       <c r="D29">
-        <v>82.66</v>
+        <v>322</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30">
-        <v>20000</v>
+        <v>1000</v>
       </c>
       <c r="B30">
-        <v>1.2370000000000001</v>
+        <v>1.4119999999999999</v>
       </c>
       <c r="C30">
-        <v>5.1159999999999997E-2</v>
+        <v>1.1220000000000001</v>
       </c>
       <c r="D30">
-        <v>82.9</v>
+        <v>324.60000000000002</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31">
-        <v>30000</v>
+        <v>2000</v>
       </c>
       <c r="B31">
-        <v>1.228</v>
+        <v>1.2889999999999999</v>
       </c>
       <c r="C31">
-        <v>3.5450000000000002E-2</v>
+        <v>1.2110000000000001</v>
       </c>
       <c r="D31">
-        <v>82.92</v>
+        <v>339.3</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32">
-        <v>40000</v>
+        <v>3000</v>
       </c>
       <c r="B32">
-        <v>1.228</v>
+        <v>1.272</v>
       </c>
       <c r="C32">
-        <v>2.7369999999999998E-2</v>
+        <v>1.2290000000000001</v>
       </c>
       <c r="D32">
-        <v>83.83</v>
+        <v>346</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33">
-        <v>50000</v>
+        <v>4000</v>
       </c>
       <c r="B33">
-        <v>1.228</v>
+        <v>1.254</v>
       </c>
       <c r="C33">
-        <v>2.2440000000000002E-2</v>
+        <v>1.2290000000000001</v>
       </c>
       <c r="D33">
-        <v>84.06</v>
+        <v>348.9</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34">
-        <v>60000</v>
+        <v>5000</v>
       </c>
       <c r="B34">
-        <v>1.21</v>
+        <v>1.246</v>
       </c>
       <c r="C34">
-        <v>1.8849999999999999E-2</v>
+        <v>1.2290000000000001</v>
       </c>
       <c r="D34">
-        <v>82.44</v>
+        <v>351.8</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35">
-        <v>70000</v>
+        <v>6000</v>
       </c>
       <c r="B35">
-        <v>1.202</v>
+        <v>1.246</v>
       </c>
       <c r="C35">
-        <v>1.6150000000000001E-2</v>
+        <v>1.2290000000000001</v>
       </c>
       <c r="D35">
-        <v>81.209999999999994</v>
+        <v>352.8</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36">
-        <v>80000</v>
+        <v>7000</v>
       </c>
       <c r="B36">
-        <v>1.1930000000000001</v>
+        <v>1.246</v>
       </c>
       <c r="C36">
-        <v>1.5259999999999999E-2</v>
+        <v>1.2290000000000001</v>
       </c>
       <c r="D36">
-        <v>85.97</v>
+        <v>353.4</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37">
-        <v>90000</v>
+        <v>8000</v>
       </c>
       <c r="B37">
-        <v>1.175</v>
+        <v>1.246</v>
       </c>
       <c r="C37">
-        <v>1.256E-2</v>
+        <v>1.2290000000000001</v>
       </c>
       <c r="D37">
-        <v>81.64</v>
+        <v>354.3</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38">
+        <v>9000</v>
+      </c>
+      <c r="B38">
+        <v>1.2370000000000001</v>
+      </c>
+      <c r="C38">
+        <v>1.238</v>
+      </c>
+      <c r="D38">
+        <v>354.6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>10000</v>
+      </c>
+      <c r="B39">
+        <v>1.2370000000000001</v>
+      </c>
+      <c r="C39">
+        <v>1.2290000000000001</v>
+      </c>
+      <c r="D39">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>20000</v>
+      </c>
+      <c r="B40">
+        <v>1.2370000000000001</v>
+      </c>
+      <c r="C40">
+        <v>1.238</v>
+      </c>
+      <c r="D40">
+        <v>357.7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A41">
+        <v>50000</v>
+      </c>
+      <c r="B41">
+        <v>1.228</v>
+      </c>
+      <c r="C41">
+        <v>1.22</v>
+      </c>
+      <c r="D41">
+        <v>359.1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A42">
         <v>100000</v>
       </c>
-      <c r="B38">
+      <c r="B42">
+        <v>1.1579999999999999</v>
+      </c>
+      <c r="C42">
+        <v>1.1579999999999999</v>
+      </c>
+      <c r="D42">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>3</v>
+      </c>
+      <c r="B76" t="s">
+        <v>4</v>
+      </c>
+      <c r="C76" t="s">
+        <v>5</v>
+      </c>
+      <c r="D76" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A77">
+        <v>100</v>
+      </c>
+      <c r="B77">
+        <v>1.97</v>
+      </c>
+      <c r="C77">
+        <v>1.9239999999999999</v>
+      </c>
+      <c r="D77">
+        <v>8.1110000000000007</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A78">
+        <v>200</v>
+      </c>
+      <c r="B78">
+        <v>1.899</v>
+      </c>
+      <c r="C78">
+        <v>1.7989999999999999</v>
+      </c>
+      <c r="D78">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A79">
+        <v>300</v>
+      </c>
+      <c r="B79">
+        <v>1.794</v>
+      </c>
+      <c r="C79">
+        <v>1.63</v>
+      </c>
+      <c r="D79">
+        <v>21.97</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A80">
+        <v>400</v>
+      </c>
+      <c r="B80">
+        <v>1.706</v>
+      </c>
+      <c r="C80">
+        <v>1.478</v>
+      </c>
+      <c r="D80">
+        <v>26.54</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A81">
+        <v>500</v>
+      </c>
+      <c r="B81">
+        <v>1.635</v>
+      </c>
+      <c r="C81">
+        <v>1.3180000000000001</v>
+      </c>
+      <c r="D81">
+        <v>31.95</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A82">
+        <v>600</v>
+      </c>
+      <c r="B82">
+        <v>1.5649999999999999</v>
+      </c>
+      <c r="C82">
+        <v>1.1930000000000001</v>
+      </c>
+      <c r="D82">
+        <v>36.9</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A83">
+        <v>700</v>
+      </c>
+      <c r="B83">
+        <v>1.53</v>
+      </c>
+      <c r="C83">
+        <v>1.0780000000000001</v>
+      </c>
+      <c r="D83">
+        <v>40.520000000000003</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A84">
+        <v>800</v>
+      </c>
+      <c r="B84">
+        <v>1.4770000000000001</v>
+      </c>
+      <c r="C84">
+        <v>0.98850000000000005</v>
+      </c>
+      <c r="D84">
+        <v>46.42</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A85">
+        <v>900</v>
+      </c>
+      <c r="B85">
+        <v>1.4419999999999999</v>
+      </c>
+      <c r="C85">
+        <v>0.98839999999999995</v>
+      </c>
+      <c r="D85">
+        <v>49.76</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A86">
+        <v>1000</v>
+      </c>
+      <c r="B86">
+        <v>1.4239999999999999</v>
+      </c>
+      <c r="C86">
+        <v>0.83709999999999996</v>
+      </c>
+      <c r="D86">
+        <v>50.84</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A87">
+        <v>2000</v>
+      </c>
+      <c r="B87">
+        <v>1.319</v>
+      </c>
+      <c r="C87">
+        <v>0.46310000000000001</v>
+      </c>
+      <c r="D87">
+        <v>68.010000000000005</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A88">
+        <v>3000</v>
+      </c>
+      <c r="B88">
+        <v>1.284</v>
+      </c>
+      <c r="C88">
+        <v>0.3206</v>
+      </c>
+      <c r="D88">
+        <v>75.540000000000006</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A89">
+        <v>4000</v>
+      </c>
+      <c r="B89">
+        <v>1.246</v>
+      </c>
+      <c r="C89">
+        <v>0.24060000000000001</v>
+      </c>
+      <c r="D89">
+        <v>77.290000000000006</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A90">
+        <v>5000</v>
+      </c>
+      <c r="B90">
+        <v>1.246</v>
+      </c>
+      <c r="C90">
+        <v>0.19420000000000001</v>
+      </c>
+      <c r="D90">
+        <v>79.92</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A91">
+        <v>6000</v>
+      </c>
+      <c r="B91">
+        <v>1.246</v>
+      </c>
+      <c r="C91">
+        <v>0.16220000000000001</v>
+      </c>
+      <c r="D91">
+        <v>79.63</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A92">
+        <v>7000</v>
+      </c>
+      <c r="B92">
+        <v>1.2370000000000001</v>
+      </c>
+      <c r="C92">
+        <v>0.1416</v>
+      </c>
+      <c r="D92">
+        <v>80.25</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A93">
+        <v>8000</v>
+      </c>
+      <c r="B93">
+        <v>1.2370000000000001</v>
+      </c>
+      <c r="C93">
+        <v>0.1255</v>
+      </c>
+      <c r="D93">
+        <v>81.16</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A94">
+        <v>9000</v>
+      </c>
+      <c r="B94">
+        <v>1.2370000000000001</v>
+      </c>
+      <c r="C94">
+        <v>0.11020000000000001</v>
+      </c>
+      <c r="D94">
+        <v>82.03</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A95">
+        <v>10000</v>
+      </c>
+      <c r="B95">
+        <v>1.2370000000000001</v>
+      </c>
+      <c r="C95">
+        <v>9.9479999999999999E-2</v>
+      </c>
+      <c r="D95">
+        <v>82.66</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A96">
+        <v>20000</v>
+      </c>
+      <c r="B96">
+        <v>1.2370000000000001</v>
+      </c>
+      <c r="C96">
+        <v>5.1159999999999997E-2</v>
+      </c>
+      <c r="D96">
+        <v>82.9</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A97">
+        <v>30000</v>
+      </c>
+      <c r="B97">
+        <v>1.228</v>
+      </c>
+      <c r="C97">
+        <v>3.5450000000000002E-2</v>
+      </c>
+      <c r="D97">
+        <v>82.92</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A98">
+        <v>40000</v>
+      </c>
+      <c r="B98">
+        <v>1.228</v>
+      </c>
+      <c r="C98">
+        <v>2.7369999999999998E-2</v>
+      </c>
+      <c r="D98">
+        <v>83.83</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A99">
+        <v>50000</v>
+      </c>
+      <c r="B99">
+        <v>1.228</v>
+      </c>
+      <c r="C99">
+        <v>2.2440000000000002E-2</v>
+      </c>
+      <c r="D99">
+        <v>84.06</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A100">
+        <v>60000</v>
+      </c>
+      <c r="B100">
+        <v>1.21</v>
+      </c>
+      <c r="C100">
+        <v>1.8849999999999999E-2</v>
+      </c>
+      <c r="D100">
+        <v>82.44</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A101">
+        <v>70000</v>
+      </c>
+      <c r="B101">
+        <v>1.202</v>
+      </c>
+      <c r="C101">
+        <v>1.6150000000000001E-2</v>
+      </c>
+      <c r="D101">
+        <v>81.209999999999994</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A102">
+        <v>80000</v>
+      </c>
+      <c r="B102">
+        <v>1.1930000000000001</v>
+      </c>
+      <c r="C102">
+        <v>1.5259999999999999E-2</v>
+      </c>
+      <c r="D102">
+        <v>85.97</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A103">
+        <v>90000</v>
+      </c>
+      <c r="B103">
+        <v>1.175</v>
+      </c>
+      <c r="C103">
+        <v>1.256E-2</v>
+      </c>
+      <c r="D103">
+        <v>81.64</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A104">
+        <v>100000</v>
+      </c>
+      <c r="B104">
         <v>1.149</v>
       </c>
-      <c r="C38">
+      <c r="C104">
         <v>1.077E-2</v>
       </c>
-      <c r="D38">
+      <c r="D104">
         <v>82.72</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/GP2/Versuch_E12/Messwerte_E12.xlsx
+++ b/GP2/Versuch_E12/Messwerte_E12.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fynnlucca/Documents/Grundpraktikum-1/GP2/Versuch_E12/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA29BF65-4A2D-B546-96D5-0C30F132DDDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EFCD78E-D1C1-FF44-9940-E82B4755C502}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20000" yWindow="3280" windowWidth="28040" windowHeight="17180" xr2:uid="{C0443A9E-E164-B441-9430-21559BD42383}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{C0443A9E-E164-B441-9430-21559BD42383}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="16">
   <si>
     <t>Versuch E12</t>
   </si>
@@ -56,9 +56,6 @@
     <t>U_R [V]</t>
   </si>
   <si>
-    <t>R = 1kOhm</t>
-  </si>
-  <si>
     <t>theta [°]</t>
   </si>
   <si>
@@ -81,6 +78,12 @@
   </si>
   <si>
     <t>A</t>
+  </si>
+  <si>
+    <t>R = 986 Ohm</t>
+  </si>
+  <si>
+    <t>Gemessen kondensator: 229.9 nF</t>
   </si>
 </sst>
 </file>
@@ -472,33 +475,36 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="D9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" t="s">
         <v>13</v>
-      </c>
-      <c r="C10" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
@@ -512,7 +518,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
@@ -951,7 +957,7 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.2">
@@ -965,7 +971,7 @@
         <v>5</v>
       </c>
       <c r="D76" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.2">

--- a/GP2/Versuch_E12/Messwerte_E12.xlsx
+++ b/GP2/Versuch_E12/Messwerte_E12.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fynnlucca/Documents/Grundpraktikum-1/GP2/Versuch_E12/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EFCD78E-D1C1-FF44-9940-E82B4755C502}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EE20ADB-15D9-D046-A002-9B2E8ECCA65B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{C0443A9E-E164-B441-9430-21559BD42383}"/>
+    <workbookView xWindow="20020" yWindow="3000" windowWidth="28040" windowHeight="17180" xr2:uid="{C0443A9E-E164-B441-9430-21559BD42383}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="18">
   <si>
     <t>Versuch E12</t>
   </si>
@@ -84,6 +84,12 @@
   </si>
   <si>
     <t>Gemessen kondensator: 229.9 nF</t>
+  </si>
+  <si>
+    <t>Aufgabe 2</t>
+  </si>
+  <si>
+    <t>R= 986 Ohm</t>
   </si>
 </sst>
 </file>
@@ -455,25 +461,36 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5060539-FDFE-EB46-A872-C3D23F847888}">
-  <dimension ref="A1:D104"/>
+  <dimension ref="A1:N104"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="K4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="K5" t="s">
+        <v>2</v>
+      </c>
+      <c r="L5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -481,33 +498,42 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>8</v>
       </c>
       <c r="D8" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="K8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D9" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
         <v>12</v>
       </c>
       <c r="C10" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="L10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -520,8 +546,20 @@
       <c r="D11" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="K11" t="s">
+        <v>3</v>
+      </c>
+      <c r="L11" t="s">
+        <v>4</v>
+      </c>
+      <c r="M11" t="s">
+        <v>5</v>
+      </c>
+      <c r="N11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>10</v>
       </c>
@@ -534,8 +572,20 @@
       <c r="D12">
         <v>84.43</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="K12">
+        <v>100</v>
+      </c>
+      <c r="L12">
+        <v>1.2370000000000001</v>
+      </c>
+      <c r="M12">
+        <v>1.238</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>20</v>
       </c>
@@ -548,8 +598,20 @@
       <c r="D13">
         <v>88.23</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="K13">
+        <v>200</v>
+      </c>
+      <c r="L13">
+        <v>1.2370000000000001</v>
+      </c>
+      <c r="M13">
+        <v>1.238</v>
+      </c>
+      <c r="N13">
+        <v>0.36799999999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>30</v>
       </c>
@@ -562,8 +624,20 @@
       <c r="D14">
         <v>276.5</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="K14">
+        <v>300</v>
+      </c>
+      <c r="L14">
+        <v>1.246</v>
+      </c>
+      <c r="M14">
+        <v>1.238</v>
+      </c>
+      <c r="N14">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>40</v>
       </c>
@@ -576,8 +650,20 @@
       <c r="D15">
         <v>275.3</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="K15">
+        <v>400</v>
+      </c>
+      <c r="L15">
+        <v>1.2370000000000001</v>
+      </c>
+      <c r="M15">
+        <v>1.2290000000000001</v>
+      </c>
+      <c r="N15">
+        <v>0.246</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>50</v>
       </c>
@@ -590,8 +676,20 @@
       <c r="D16">
         <v>276.5</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="K16">
+        <v>500</v>
+      </c>
+      <c r="L16">
+        <v>1.2370000000000001</v>
+      </c>
+      <c r="M16">
+        <v>1.2290000000000001</v>
+      </c>
+      <c r="N16">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>60</v>
       </c>
@@ -604,8 +702,20 @@
       <c r="D17">
         <v>276.3</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="K17">
+        <v>600</v>
+      </c>
+      <c r="L17">
+        <v>1.2370000000000001</v>
+      </c>
+      <c r="M17">
+        <v>1.238</v>
+      </c>
+      <c r="N17">
+        <v>0.442</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>70</v>
       </c>
@@ -618,8 +728,20 @@
       <c r="D18">
         <v>278.8</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="K18">
+        <v>700</v>
+      </c>
+      <c r="L18">
+        <v>1.2370000000000001</v>
+      </c>
+      <c r="M18">
+        <v>1.2290000000000001</v>
+      </c>
+      <c r="N18">
+        <v>0.41399999999999998</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>80</v>
       </c>
@@ -632,8 +754,20 @@
       <c r="D19">
         <v>278.8</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="K19">
+        <v>800</v>
+      </c>
+      <c r="L19">
+        <v>1.2370000000000001</v>
+      </c>
+      <c r="M19">
+        <v>1.2290000000000001</v>
+      </c>
+      <c r="N19">
+        <v>0.246</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>90</v>
       </c>
@@ -646,8 +780,20 @@
       <c r="D20">
         <v>280.39999999999998</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="K20">
+        <v>900</v>
+      </c>
+      <c r="L20">
+        <v>1.2370000000000001</v>
+      </c>
+      <c r="M20">
+        <v>1.238</v>
+      </c>
+      <c r="N20">
+        <v>0.41399999999999998</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>100</v>
       </c>
@@ -660,8 +806,20 @@
       <c r="D21">
         <v>281.10000000000002</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="K21">
+        <v>1000</v>
+      </c>
+      <c r="L21">
+        <v>1.2370000000000001</v>
+      </c>
+      <c r="M21">
+        <v>1.2290000000000001</v>
+      </c>
+      <c r="N21">
+        <v>0.307</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>200</v>
       </c>
@@ -674,8 +832,20 @@
       <c r="D22">
         <v>288.5</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="K22">
+        <v>2000</v>
+      </c>
+      <c r="L22">
+        <v>1.2370000000000001</v>
+      </c>
+      <c r="M22">
+        <v>1.2290000000000001</v>
+      </c>
+      <c r="N22">
+        <v>0.76800000000000002</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>300</v>
       </c>
@@ -688,8 +858,20 @@
       <c r="D23">
         <v>294.7</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="K23">
+        <v>3000</v>
+      </c>
+      <c r="L23">
+        <v>1.2370000000000001</v>
+      </c>
+      <c r="M23">
+        <v>1.2290000000000001</v>
+      </c>
+      <c r="N23">
+        <v>1.1060000000000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>400</v>
       </c>
@@ -702,8 +884,20 @@
       <c r="D24">
         <v>300.8</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="K24">
+        <v>4000</v>
+      </c>
+      <c r="L24">
+        <v>1.2370000000000001</v>
+      </c>
+      <c r="M24">
+        <v>1.2290000000000001</v>
+      </c>
+      <c r="N24">
+        <v>1.228</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>500</v>
       </c>
@@ -716,8 +910,20 @@
       <c r="D25">
         <v>305.89999999999998</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="K25">
+        <v>5000</v>
+      </c>
+      <c r="L25">
+        <v>1.2370000000000001</v>
+      </c>
+      <c r="M25">
+        <v>1.238</v>
+      </c>
+      <c r="N25">
+        <v>1.871</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>600</v>
       </c>
@@ -730,8 +936,20 @@
       <c r="D26">
         <v>311.7</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="K26">
+        <v>6000</v>
+      </c>
+      <c r="L26">
+        <v>1.2370000000000001</v>
+      </c>
+      <c r="M26">
+        <v>1.2290000000000001</v>
+      </c>
+      <c r="N26">
+        <v>2.0739999999999998</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>700</v>
       </c>
@@ -744,8 +962,20 @@
       <c r="D27">
         <v>315.3</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="K27">
+        <v>7000</v>
+      </c>
+      <c r="L27">
+        <v>1.2370000000000001</v>
+      </c>
+      <c r="M27">
+        <v>1.2290000000000001</v>
+      </c>
+      <c r="N27">
+        <v>2.6880000000000002</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>800</v>
       </c>
@@ -758,8 +988,20 @@
       <c r="D28">
         <v>318.8</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="K28">
+        <v>8000</v>
+      </c>
+      <c r="L28">
+        <v>1.2370000000000001</v>
+      </c>
+      <c r="M28">
+        <v>1.2290000000000001</v>
+      </c>
+      <c r="N28">
+        <v>2.3050000000000002</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>900</v>
       </c>
@@ -772,8 +1014,20 @@
       <c r="D29">
         <v>322</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="K29">
+        <v>9000</v>
+      </c>
+      <c r="L29">
+        <v>1.2370000000000001</v>
+      </c>
+      <c r="M29">
+        <v>1.2290000000000001</v>
+      </c>
+      <c r="N29">
+        <v>2.5910000000000002</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>1000</v>
       </c>
@@ -786,8 +1040,20 @@
       <c r="D30">
         <v>324.60000000000002</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="K30">
+        <v>10000</v>
+      </c>
+      <c r="L30">
+        <v>1.2370000000000001</v>
+      </c>
+      <c r="M30">
+        <v>1.2290000000000001</v>
+      </c>
+      <c r="N30">
+        <v>3.456</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>2000</v>
       </c>
@@ -800,8 +1066,20 @@
       <c r="D31">
         <v>339.3</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="K31">
+        <v>20000</v>
+      </c>
+      <c r="L31">
+        <v>1.2370000000000001</v>
+      </c>
+      <c r="M31">
+        <v>1.2290000000000001</v>
+      </c>
+      <c r="N31">
+        <v>6.7190000000000003</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>3000</v>
       </c>
@@ -814,8 +1092,20 @@
       <c r="D32">
         <v>346</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="K32">
+        <v>30000</v>
+      </c>
+      <c r="L32">
+        <v>1.2370000000000001</v>
+      </c>
+      <c r="M32">
+        <v>1.2290000000000001</v>
+      </c>
+      <c r="N32">
+        <v>10.72</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>4000</v>
       </c>
@@ -828,8 +1118,20 @@
       <c r="D33">
         <v>348.9</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="K33">
+        <v>40000</v>
+      </c>
+      <c r="L33">
+        <v>1.254</v>
+      </c>
+      <c r="M33">
+        <v>1.22</v>
+      </c>
+      <c r="N33">
+        <v>14.02</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>5000</v>
       </c>
@@ -842,8 +1144,20 @@
       <c r="D34">
         <v>351.8</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="K34">
+        <v>50000</v>
+      </c>
+      <c r="L34">
+        <v>1.2629999999999999</v>
+      </c>
+      <c r="M34">
+        <v>1.202</v>
+      </c>
+      <c r="N34">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>6000</v>
       </c>
@@ -856,8 +1170,20 @@
       <c r="D35">
         <v>352.8</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="K35">
+        <v>60000</v>
+      </c>
+      <c r="L35">
+        <v>1.2629999999999999</v>
+      </c>
+      <c r="M35">
+        <v>1.1839999999999999</v>
+      </c>
+      <c r="N35">
+        <v>21.08</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>7000</v>
       </c>
@@ -870,8 +1196,20 @@
       <c r="D36">
         <v>353.4</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="K36">
+        <v>70000</v>
+      </c>
+      <c r="L36">
+        <v>1.272</v>
+      </c>
+      <c r="M36">
+        <v>1.167</v>
+      </c>
+      <c r="N36">
+        <v>24.86</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>8000</v>
       </c>
@@ -884,8 +1222,20 @@
       <c r="D37">
         <v>354.3</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="K37">
+        <v>80000</v>
+      </c>
+      <c r="L37">
+        <v>1.2809999999999999</v>
+      </c>
+      <c r="M37">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="N37">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>9000</v>
       </c>
@@ -898,8 +1248,20 @@
       <c r="D38">
         <v>354.6</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="K38">
+        <v>90000</v>
+      </c>
+      <c r="L38">
+        <v>1.2809999999999999</v>
+      </c>
+      <c r="M38">
+        <v>1.113</v>
+      </c>
+      <c r="N38">
+        <v>30.75</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>10000</v>
       </c>
@@ -912,8 +1274,20 @@
       <c r="D39">
         <v>355</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="K39">
+        <v>100000</v>
+      </c>
+      <c r="L39">
+        <v>1.272</v>
+      </c>
+      <c r="M39">
+        <v>1.0780000000000001</v>
+      </c>
+      <c r="N39">
+        <v>33.119999999999997</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>20000</v>
       </c>
@@ -927,7 +1301,7 @@
         <v>357.7</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>50000</v>
       </c>
@@ -941,7 +1315,7 @@
         <v>359.1</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>100000</v>
       </c>

--- a/GP2/Versuch_E12/Messwerte_E12.xlsx
+++ b/GP2/Versuch_E12/Messwerte_E12.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fynnlucca/Documents/Grundpraktikum-1/GP2/Versuch_E12/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EE20ADB-15D9-D046-A002-9B2E8ECCA65B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DF4B542-61C0-1847-B1FB-3AF23D315022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20020" yWindow="3000" windowWidth="28040" windowHeight="17180" xr2:uid="{C0443A9E-E164-B441-9430-21559BD42383}"/>
+    <workbookView xWindow="8620" yWindow="2980" windowWidth="28040" windowHeight="17180" xr2:uid="{C0443A9E-E164-B441-9430-21559BD42383}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="20">
   <si>
     <t>Versuch E12</t>
   </si>
@@ -90,6 +90,12 @@
   </si>
   <si>
     <t>R= 986 Ohm</t>
+  </si>
+  <si>
+    <t>Aufgabe 3</t>
+  </si>
+  <si>
+    <t>Aufgabe 4</t>
   </si>
 </sst>
 </file>
@@ -461,25 +467,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5060539-FDFE-EB46-A872-C3D23F847888}">
-  <dimension ref="A1:N104"/>
+  <dimension ref="A1:AE104"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.2">
       <c r="K4" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R4" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -489,8 +501,26 @@
       <c r="L5" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R5" t="s">
+        <v>2</v>
+      </c>
+      <c r="S5" t="s">
+        <v>17</v>
+      </c>
+      <c r="T5" t="s">
+        <v>15</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>17</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -498,12 +528,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -514,12 +544,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D9" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
         <v>12</v>
       </c>
@@ -532,8 +562,20 @@
       <c r="M10" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="S10" t="s">
+        <v>12</v>
+      </c>
+      <c r="T10" t="s">
+        <v>13</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -558,8 +600,32 @@
       <c r="N11" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R11" t="s">
+        <v>3</v>
+      </c>
+      <c r="S11" t="s">
+        <v>4</v>
+      </c>
+      <c r="T11" t="s">
+        <v>5</v>
+      </c>
+      <c r="U11" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>10</v>
       </c>
@@ -584,8 +650,32 @@
       <c r="N12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R12">
+        <v>10</v>
+      </c>
+      <c r="S12">
+        <v>1.97</v>
+      </c>
+      <c r="T12">
+        <v>3.5900000000000001E-2</v>
+      </c>
+      <c r="U12">
+        <v>87.42</v>
+      </c>
+      <c r="AB12">
+        <v>10</v>
+      </c>
+      <c r="AC12">
+        <v>1.2190000000000001</v>
+      </c>
+      <c r="AD12">
+        <v>1.2290000000000001</v>
+      </c>
+      <c r="AE12">
+        <v>359.8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>20</v>
       </c>
@@ -610,8 +700,32 @@
       <c r="N13">
         <v>0.36799999999999999</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R13">
+        <v>20</v>
+      </c>
+      <c r="S13">
+        <v>1.9870000000000001</v>
+      </c>
+      <c r="T13">
+        <v>6.5070000000000003E-2</v>
+      </c>
+      <c r="U13">
+        <v>273.7</v>
+      </c>
+      <c r="AB13">
+        <v>20</v>
+      </c>
+      <c r="AC13">
+        <v>1.2370000000000001</v>
+      </c>
+      <c r="AD13">
+        <v>1.238</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>30</v>
       </c>
@@ -636,8 +750,32 @@
       <c r="N14">
         <v>0.11</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R14">
+        <v>30</v>
+      </c>
+      <c r="S14">
+        <v>1.9870000000000001</v>
+      </c>
+      <c r="T14">
+        <v>9.3799999999999994E-2</v>
+      </c>
+      <c r="U14">
+        <v>276.5</v>
+      </c>
+      <c r="AB14">
+        <v>30</v>
+      </c>
+      <c r="AC14">
+        <v>1.246</v>
+      </c>
+      <c r="AD14">
+        <v>1.238</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>40</v>
       </c>
@@ -662,8 +800,32 @@
       <c r="N15">
         <v>0.246</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R15">
+        <v>40</v>
+      </c>
+      <c r="S15">
+        <v>1.9870000000000001</v>
+      </c>
+      <c r="T15">
+        <v>0.12189999999999999</v>
+      </c>
+      <c r="U15">
+        <v>275.39999999999998</v>
+      </c>
+      <c r="AB15">
+        <v>40</v>
+      </c>
+      <c r="AC15">
+        <v>1.2370000000000001</v>
+      </c>
+      <c r="AD15">
+        <v>1.238</v>
+      </c>
+      <c r="AE15">
+        <v>359.8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>50</v>
       </c>
@@ -688,8 +850,32 @@
       <c r="N16">
         <v>0.23</v>
       </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R16">
+        <v>50</v>
+      </c>
+      <c r="S16">
+        <v>1.9870000000000001</v>
+      </c>
+      <c r="T16">
+        <v>0.15060000000000001</v>
+      </c>
+      <c r="U16">
+        <v>275.2</v>
+      </c>
+      <c r="AB16">
+        <v>50</v>
+      </c>
+      <c r="AC16">
+        <v>1.2370000000000001</v>
+      </c>
+      <c r="AD16">
+        <v>1.238</v>
+      </c>
+      <c r="AE16">
+        <v>0.184</v>
+      </c>
+    </row>
+    <row r="17" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>60</v>
       </c>
@@ -714,8 +900,32 @@
       <c r="N17">
         <v>0.442</v>
       </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R17">
+        <v>60</v>
+      </c>
+      <c r="S17">
+        <v>1.97</v>
+      </c>
+      <c r="T17">
+        <v>0.1757</v>
+      </c>
+      <c r="U17">
+        <v>278.10000000000002</v>
+      </c>
+      <c r="AB17">
+        <v>60</v>
+      </c>
+      <c r="AC17">
+        <v>1.2370000000000001</v>
+      </c>
+      <c r="AD17">
+        <v>1.238</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>70</v>
       </c>
@@ -740,8 +950,32 @@
       <c r="N18">
         <v>0.41399999999999998</v>
       </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R18">
+        <v>70</v>
+      </c>
+      <c r="S18">
+        <v>1.97</v>
+      </c>
+      <c r="T18">
+        <v>0.20319999999999999</v>
+      </c>
+      <c r="U18">
+        <v>278.89999999999998</v>
+      </c>
+      <c r="AB18">
+        <v>70</v>
+      </c>
+      <c r="AC18">
+        <v>1.2370000000000001</v>
+      </c>
+      <c r="AD18">
+        <v>1.238</v>
+      </c>
+      <c r="AE18">
+        <v>0.34399999999999997</v>
+      </c>
+    </row>
+    <row r="19" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>80</v>
       </c>
@@ -766,8 +1000,32 @@
       <c r="N19">
         <v>0.246</v>
       </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R19">
+        <v>80</v>
+      </c>
+      <c r="S19">
+        <v>1.97</v>
+      </c>
+      <c r="T19">
+        <v>0.23169999999999999</v>
+      </c>
+      <c r="U19">
+        <v>280</v>
+      </c>
+      <c r="AB19">
+        <v>80</v>
+      </c>
+      <c r="AC19">
+        <v>1.2370000000000001</v>
+      </c>
+      <c r="AD19">
+        <v>1.238</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>90</v>
       </c>
@@ -792,8 +1050,32 @@
       <c r="N20">
         <v>0.41399999999999998</v>
       </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R20">
+        <v>90</v>
+      </c>
+      <c r="S20">
+        <v>1.97</v>
+      </c>
+      <c r="T20">
+        <v>0.25659999999999999</v>
+      </c>
+      <c r="U20">
+        <v>280.39999999999998</v>
+      </c>
+      <c r="AB20">
+        <v>90</v>
+      </c>
+      <c r="AC20">
+        <v>1.246</v>
+      </c>
+      <c r="AD20">
+        <v>1.238</v>
+      </c>
+      <c r="AE20">
+        <v>0.82899999999999996</v>
+      </c>
+    </row>
+    <row r="21" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>100</v>
       </c>
@@ -818,8 +1100,32 @@
       <c r="N21">
         <v>0.307</v>
       </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R21">
+        <v>100</v>
+      </c>
+      <c r="S21">
+        <v>1.97</v>
+      </c>
+      <c r="T21">
+        <v>0.2833</v>
+      </c>
+      <c r="U21">
+        <v>280.89999999999998</v>
+      </c>
+      <c r="AB21">
+        <v>100</v>
+      </c>
+      <c r="AC21">
+        <v>1.2370000000000001</v>
+      </c>
+      <c r="AD21">
+        <v>1.238</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>200</v>
       </c>
@@ -844,8 +1150,32 @@
       <c r="N22">
         <v>0.76800000000000002</v>
       </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R22">
+        <v>200</v>
+      </c>
+      <c r="S22">
+        <v>1.877</v>
+      </c>
+      <c r="T22">
+        <v>0.51659999999999995</v>
+      </c>
+      <c r="U22">
+        <v>289</v>
+      </c>
+      <c r="AB22">
+        <v>200</v>
+      </c>
+      <c r="AC22">
+        <v>1.2370000000000001</v>
+      </c>
+      <c r="AD22">
+        <v>1.238</v>
+      </c>
+      <c r="AE22">
+        <v>0.36799999999999999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>300</v>
       </c>
@@ -870,8 +1200,32 @@
       <c r="N23">
         <v>1.1060000000000001</v>
       </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R23">
+        <v>300</v>
+      </c>
+      <c r="S23">
+        <v>1.7809999999999999</v>
+      </c>
+      <c r="T23">
+        <v>0.69030000000000002</v>
+      </c>
+      <c r="U23">
+        <v>295.5</v>
+      </c>
+      <c r="AB23">
+        <v>300</v>
+      </c>
+      <c r="AC23">
+        <v>1.2370000000000001</v>
+      </c>
+      <c r="AD23">
+        <v>1.238</v>
+      </c>
+      <c r="AE23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>400</v>
       </c>
@@ -896,8 +1250,32 @@
       <c r="N24">
         <v>1.228</v>
       </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R24">
+        <v>400</v>
+      </c>
+      <c r="S24">
+        <v>1.6930000000000001</v>
+      </c>
+      <c r="T24">
+        <v>0.81940000000000002</v>
+      </c>
+      <c r="U24">
+        <v>301</v>
+      </c>
+      <c r="AB24">
+        <v>400</v>
+      </c>
+      <c r="AC24">
+        <v>1.246</v>
+      </c>
+      <c r="AD24">
+        <v>1.238</v>
+      </c>
+      <c r="AE24">
+        <v>0.246</v>
+      </c>
+    </row>
+    <row r="25" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>500</v>
       </c>
@@ -922,8 +1300,32 @@
       <c r="N25">
         <v>1.871</v>
       </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R25">
+        <v>500</v>
+      </c>
+      <c r="S25">
+        <v>1.6140000000000001</v>
+      </c>
+      <c r="T25">
+        <v>0.91739999999999999</v>
+      </c>
+      <c r="U25">
+        <v>306.89999999999998</v>
+      </c>
+      <c r="AB25">
+        <v>500</v>
+      </c>
+      <c r="AC25">
+        <v>1.2370000000000001</v>
+      </c>
+      <c r="AD25">
+        <v>1.238</v>
+      </c>
+      <c r="AE25">
+        <v>0.34599999999999997</v>
+      </c>
+    </row>
+    <row r="26" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>600</v>
       </c>
@@ -948,8 +1350,32 @@
       <c r="N26">
         <v>2.0739999999999998</v>
       </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R26">
+        <v>600</v>
+      </c>
+      <c r="S26">
+        <v>1.5609999999999999</v>
+      </c>
+      <c r="T26">
+        <v>0.98850000000000005</v>
+      </c>
+      <c r="U26">
+        <v>311.89999999999998</v>
+      </c>
+      <c r="AB26">
+        <v>600</v>
+      </c>
+      <c r="AC26">
+        <v>1.2370000000000001</v>
+      </c>
+      <c r="AD26">
+        <v>1.238</v>
+      </c>
+      <c r="AE26">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>700</v>
       </c>
@@ -974,8 +1400,32 @@
       <c r="N27">
         <v>2.6880000000000002</v>
       </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R27">
+        <v>700</v>
+      </c>
+      <c r="S27">
+        <v>1.5089999999999999</v>
+      </c>
+      <c r="T27">
+        <v>1.0509999999999999</v>
+      </c>
+      <c r="U27">
+        <v>315.89999999999998</v>
+      </c>
+      <c r="AB27">
+        <v>700</v>
+      </c>
+      <c r="AC27">
+        <v>1.2370000000000001</v>
+      </c>
+      <c r="AD27">
+        <v>1.238</v>
+      </c>
+      <c r="AE27">
+        <v>0.53800000000000003</v>
+      </c>
+    </row>
+    <row r="28" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>800</v>
       </c>
@@ -1000,8 +1450,32 @@
       <c r="N28">
         <v>2.3050000000000002</v>
       </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R28">
+        <v>800</v>
+      </c>
+      <c r="S28">
+        <v>1.4650000000000001</v>
+      </c>
+      <c r="T28">
+        <v>1.069</v>
+      </c>
+      <c r="U28">
+        <v>319.2</v>
+      </c>
+      <c r="AB28">
+        <v>800</v>
+      </c>
+      <c r="AC28">
+        <v>1.2370000000000001</v>
+      </c>
+      <c r="AD28">
+        <v>1.238</v>
+      </c>
+      <c r="AE28">
+        <v>0.49199999999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>900</v>
       </c>
@@ -1026,8 +1500,32 @@
       <c r="N29">
         <v>2.5910000000000002</v>
       </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R29">
+        <v>900</v>
+      </c>
+      <c r="S29">
+        <v>1.4390000000000001</v>
+      </c>
+      <c r="T29">
+        <v>1.1040000000000001</v>
+      </c>
+      <c r="U29">
+        <v>322.89999999999998</v>
+      </c>
+      <c r="AB29">
+        <v>900</v>
+      </c>
+      <c r="AC29">
+        <v>1.2370000000000001</v>
+      </c>
+      <c r="AD29">
+        <v>1.238</v>
+      </c>
+      <c r="AE29">
+        <v>0.41499999999999998</v>
+      </c>
+    </row>
+    <row r="30" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>1000</v>
       </c>
@@ -1052,8 +1550,32 @@
       <c r="N30">
         <v>3.456</v>
       </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R30">
+        <v>1000</v>
+      </c>
+      <c r="S30">
+        <v>1.4119999999999999</v>
+      </c>
+      <c r="T30">
+        <v>1.1220000000000001</v>
+      </c>
+      <c r="U30">
+        <v>325.10000000000002</v>
+      </c>
+      <c r="AB30">
+        <v>1000</v>
+      </c>
+      <c r="AC30">
+        <v>1.2370000000000001</v>
+      </c>
+      <c r="AD30">
+        <v>1.238</v>
+      </c>
+      <c r="AE30">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="31" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>2000</v>
       </c>
@@ -1078,8 +1600,32 @@
       <c r="N31">
         <v>6.7190000000000003</v>
       </c>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R31">
+        <v>2000</v>
+      </c>
+      <c r="S31">
+        <v>1.298</v>
+      </c>
+      <c r="T31">
+        <v>1.2110000000000001</v>
+      </c>
+      <c r="U31">
+        <v>340.6</v>
+      </c>
+      <c r="AB31">
+        <v>2000</v>
+      </c>
+      <c r="AC31">
+        <v>1.2370000000000001</v>
+      </c>
+      <c r="AD31">
+        <v>1.238</v>
+      </c>
+      <c r="AE31">
+        <v>0.76800000000000002</v>
+      </c>
+    </row>
+    <row r="32" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>3000</v>
       </c>
@@ -1104,8 +1650,32 @@
       <c r="N32">
         <v>10.72</v>
       </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R32">
+        <v>3000</v>
+      </c>
+      <c r="S32">
+        <v>1.272</v>
+      </c>
+      <c r="T32">
+        <v>1.2290000000000001</v>
+      </c>
+      <c r="U32">
+        <v>347.1</v>
+      </c>
+      <c r="AB32">
+        <v>3000</v>
+      </c>
+      <c r="AC32">
+        <v>1.2370000000000001</v>
+      </c>
+      <c r="AD32">
+        <v>1.238</v>
+      </c>
+      <c r="AE32">
+        <v>1.3819999999999999</v>
+      </c>
+    </row>
+    <row r="33" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>4000</v>
       </c>
@@ -1130,8 +1700,32 @@
       <c r="N33">
         <v>14.02</v>
       </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R33">
+        <v>4000</v>
+      </c>
+      <c r="S33">
+        <v>1.254</v>
+      </c>
+      <c r="T33">
+        <v>1.2290000000000001</v>
+      </c>
+      <c r="U33">
+        <v>350.9</v>
+      </c>
+      <c r="AB33">
+        <v>4000</v>
+      </c>
+      <c r="AC33">
+        <v>1.2370000000000001</v>
+      </c>
+      <c r="AD33">
+        <v>1.2290000000000001</v>
+      </c>
+      <c r="AE33">
+        <v>1.843</v>
+      </c>
+    </row>
+    <row r="34" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>5000</v>
       </c>
@@ -1156,8 +1750,32 @@
       <c r="N34">
         <v>18</v>
       </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R34">
+        <v>5000</v>
+      </c>
+      <c r="S34">
+        <v>1.254</v>
+      </c>
+      <c r="T34">
+        <v>1.2470000000000001</v>
+      </c>
+      <c r="U34">
+        <v>353.1</v>
+      </c>
+      <c r="AB34">
+        <v>5000</v>
+      </c>
+      <c r="AC34">
+        <v>1.2370000000000001</v>
+      </c>
+      <c r="AD34">
+        <v>1.238</v>
+      </c>
+      <c r="AE34">
+        <v>2.016</v>
+      </c>
+    </row>
+    <row r="35" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>6000</v>
       </c>
@@ -1182,8 +1800,32 @@
       <c r="N35">
         <v>21.08</v>
       </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R35">
+        <v>6000</v>
+      </c>
+      <c r="S35">
+        <v>1.254</v>
+      </c>
+      <c r="T35">
+        <v>1.238</v>
+      </c>
+      <c r="U35">
+        <v>354.7</v>
+      </c>
+      <c r="AB35">
+        <v>6000</v>
+      </c>
+      <c r="AC35">
+        <v>1.2370000000000001</v>
+      </c>
+      <c r="AD35">
+        <v>1.238</v>
+      </c>
+      <c r="AE35">
+        <v>3.18</v>
+      </c>
+    </row>
+    <row r="36" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>7000</v>
       </c>
@@ -1208,8 +1850,32 @@
       <c r="N36">
         <v>24.86</v>
       </c>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R36">
+        <v>7000</v>
+      </c>
+      <c r="S36">
+        <v>1.254</v>
+      </c>
+      <c r="T36">
+        <v>1.2470000000000001</v>
+      </c>
+      <c r="U36">
+        <v>356.8</v>
+      </c>
+      <c r="AB36">
+        <v>7000</v>
+      </c>
+      <c r="AC36">
+        <v>1.246</v>
+      </c>
+      <c r="AD36">
+        <v>1.2290000000000001</v>
+      </c>
+      <c r="AE36">
+        <v>4.0339999999999998</v>
+      </c>
+    </row>
+    <row r="37" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>8000</v>
       </c>
@@ -1234,8 +1900,32 @@
       <c r="N37">
         <v>26.5</v>
       </c>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R37">
+        <v>8000</v>
+      </c>
+      <c r="S37">
+        <v>1.246</v>
+      </c>
+      <c r="T37">
+        <v>1.238</v>
+      </c>
+      <c r="U37">
+        <v>357.2</v>
+      </c>
+      <c r="AB37">
+        <v>8000</v>
+      </c>
+      <c r="AC37">
+        <v>1.246</v>
+      </c>
+      <c r="AD37">
+        <v>1.22</v>
+      </c>
+      <c r="AE37">
+        <v>6.4509999999999996</v>
+      </c>
+    </row>
+    <row r="38" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>9000</v>
       </c>
@@ -1260,8 +1950,32 @@
       <c r="N38">
         <v>30.75</v>
       </c>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R38">
+        <v>9000</v>
+      </c>
+      <c r="S38">
+        <v>1.246</v>
+      </c>
+      <c r="T38">
+        <v>1.2470000000000001</v>
+      </c>
+      <c r="U38">
+        <v>357.9</v>
+      </c>
+      <c r="AB38">
+        <v>9000</v>
+      </c>
+      <c r="AC38">
+        <v>1.254</v>
+      </c>
+      <c r="AD38">
+        <v>1.2110000000000001</v>
+      </c>
+      <c r="AE38">
+        <v>9.2040000000000006</v>
+      </c>
+    </row>
+    <row r="39" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>10000</v>
       </c>
@@ -1286,8 +2000,32 @@
       <c r="N39">
         <v>33.119999999999997</v>
       </c>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R39">
+        <v>10000</v>
+      </c>
+      <c r="S39">
+        <v>1.246</v>
+      </c>
+      <c r="T39">
+        <v>1.2470000000000001</v>
+      </c>
+      <c r="U39">
+        <v>358.7</v>
+      </c>
+      <c r="AB39">
+        <v>10000</v>
+      </c>
+      <c r="AC39">
+        <v>1.3069999999999999</v>
+      </c>
+      <c r="AD39">
+        <v>1.1579999999999999</v>
+      </c>
+      <c r="AE39">
+        <v>15.26</v>
+      </c>
+    </row>
+    <row r="40" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>20000</v>
       </c>
@@ -1300,8 +2038,32 @@
       <c r="D40">
         <v>357.7</v>
       </c>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R40">
+        <v>20000</v>
+      </c>
+      <c r="S40">
+        <v>1.246</v>
+      </c>
+      <c r="T40">
+        <v>1.238</v>
+      </c>
+      <c r="U40">
+        <v>5.5679999999999996</v>
+      </c>
+      <c r="AB40">
+        <v>20000</v>
+      </c>
+      <c r="AC40">
+        <v>1.2370000000000001</v>
+      </c>
+      <c r="AD40">
+        <v>1.2290000000000001</v>
+      </c>
+      <c r="AE40">
+        <v>356.4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>50000</v>
       </c>
@@ -1314,8 +2076,32 @@
       <c r="D41">
         <v>359.1</v>
       </c>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R41">
+        <v>30000</v>
+      </c>
+      <c r="S41">
+        <v>1.246</v>
+      </c>
+      <c r="T41">
+        <v>1.238</v>
+      </c>
+      <c r="U41">
+        <v>9.3320000000000007</v>
+      </c>
+      <c r="AB41">
+        <v>30000</v>
+      </c>
+      <c r="AC41">
+        <v>1.228</v>
+      </c>
+      <c r="AD41">
+        <v>1.2290000000000001</v>
+      </c>
+      <c r="AE41">
+        <v>357.9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>100000</v>
       </c>
@@ -1327,6 +2113,186 @@
       </c>
       <c r="D42">
         <v>360</v>
+      </c>
+      <c r="R42">
+        <v>40000</v>
+      </c>
+      <c r="S42">
+        <v>1.2629999999999999</v>
+      </c>
+      <c r="T42">
+        <v>1.22</v>
+      </c>
+      <c r="U42">
+        <v>12.87</v>
+      </c>
+      <c r="AB42">
+        <v>40000</v>
+      </c>
+      <c r="AC42">
+        <v>1.228</v>
+      </c>
+      <c r="AD42">
+        <v>1.22</v>
+      </c>
+      <c r="AE42">
+        <v>358.5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="R43">
+        <v>50000</v>
+      </c>
+      <c r="S43">
+        <v>1.2629999999999999</v>
+      </c>
+      <c r="T43">
+        <v>1.22</v>
+      </c>
+      <c r="U43">
+        <v>16.38</v>
+      </c>
+      <c r="AB43">
+        <v>50000</v>
+      </c>
+      <c r="AC43">
+        <v>1.2190000000000001</v>
+      </c>
+      <c r="AD43">
+        <v>1.22</v>
+      </c>
+      <c r="AE43">
+        <v>358.6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="R44">
+        <v>60000</v>
+      </c>
+      <c r="S44">
+        <v>1.272</v>
+      </c>
+      <c r="T44">
+        <v>1.1930000000000001</v>
+      </c>
+      <c r="U44">
+        <v>18.489999999999998</v>
+      </c>
+      <c r="AB44">
+        <v>60000</v>
+      </c>
+      <c r="AC44">
+        <v>1.21</v>
+      </c>
+      <c r="AD44">
+        <v>1.22</v>
+      </c>
+      <c r="AE44">
+        <v>359.1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="R45">
+        <v>70000</v>
+      </c>
+      <c r="S45">
+        <v>1.2809999999999999</v>
+      </c>
+      <c r="T45">
+        <v>1.1759999999999999</v>
+      </c>
+      <c r="U45">
+        <v>24.32</v>
+      </c>
+      <c r="AB45">
+        <v>70000</v>
+      </c>
+      <c r="AC45">
+        <v>1.202</v>
+      </c>
+      <c r="AD45">
+        <v>1.2110000000000001</v>
+      </c>
+      <c r="AE45">
+        <v>359.2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="R46">
+        <v>80000</v>
+      </c>
+      <c r="S46">
+        <v>1.2809999999999999</v>
+      </c>
+      <c r="T46">
+        <v>1.167</v>
+      </c>
+      <c r="U46">
+        <v>26.3</v>
+      </c>
+      <c r="AB46">
+        <v>80000</v>
+      </c>
+      <c r="AC46">
+        <v>1.1930000000000001</v>
+      </c>
+      <c r="AD46">
+        <v>1.1839999999999999</v>
+      </c>
+      <c r="AE46">
+        <v>359.7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="R47">
+        <v>90000</v>
+      </c>
+      <c r="S47">
+        <v>1.2809999999999999</v>
+      </c>
+      <c r="T47">
+        <v>1.1220000000000001</v>
+      </c>
+      <c r="U47">
+        <v>29.64</v>
+      </c>
+      <c r="AB47">
+        <v>90000</v>
+      </c>
+      <c r="AC47">
+        <v>1.175</v>
+      </c>
+      <c r="AD47">
+        <v>1.1839999999999999</v>
+      </c>
+      <c r="AE47">
+        <v>359.4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="R48">
+        <v>100000</v>
+      </c>
+      <c r="S48">
+        <v>1.2889999999999999</v>
+      </c>
+      <c r="T48">
+        <v>1.095</v>
+      </c>
+      <c r="U48">
+        <v>32.06</v>
+      </c>
+      <c r="AB48">
+        <v>100000</v>
+      </c>
+      <c r="AC48">
+        <v>1.149</v>
+      </c>
+      <c r="AD48">
+        <v>1.1579999999999999</v>
+      </c>
+      <c r="AE48">
+        <v>358.9</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.2">

--- a/GP2/Versuch_E12/Messwerte_E12.xlsx
+++ b/GP2/Versuch_E12/Messwerte_E12.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fynnlucca/Documents/Grundpraktikum-1/GP2/Versuch_E12/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DF4B542-61C0-1847-B1FB-3AF23D315022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78A71793-35A5-704C-BC56-652C06CCCE8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8620" yWindow="2980" windowWidth="28040" windowHeight="17180" xr2:uid="{C0443A9E-E164-B441-9430-21559BD42383}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{C0443A9E-E164-B441-9430-21559BD42383}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="21">
   <si>
     <t>Versuch E12</t>
   </si>
@@ -96,6 +96,9 @@
   </si>
   <si>
     <t>Aufgabe 4</t>
+  </si>
+  <si>
+    <t>d</t>
   </si>
 </sst>
 </file>
@@ -467,7 +470,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5060539-FDFE-EB46-A872-C3D23F847888}">
-  <dimension ref="A1:AE104"/>
+  <dimension ref="A1:AG104"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.2">
@@ -875,7 +878,7 @@
         <v>0.184</v>
       </c>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>60</v>
       </c>
@@ -924,8 +927,11 @@
       <c r="AE17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AG17" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>70</v>
       </c>
@@ -975,7 +981,7 @@
         <v>0.34399999999999997</v>
       </c>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>80</v>
       </c>
@@ -1025,7 +1031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>90</v>
       </c>
@@ -1075,7 +1081,7 @@
         <v>0.82899999999999996</v>
       </c>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>100</v>
       </c>
@@ -1125,7 +1131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>200</v>
       </c>
@@ -1175,7 +1181,7 @@
         <v>0.36799999999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>300</v>
       </c>
@@ -1225,7 +1231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>400</v>
       </c>
@@ -1275,7 +1281,7 @@
         <v>0.246</v>
       </c>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>500</v>
       </c>
@@ -1325,7 +1331,7 @@
         <v>0.34599999999999997</v>
       </c>
     </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>600</v>
       </c>
@@ -1375,7 +1381,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>700</v>
       </c>
@@ -1425,7 +1431,7 @@
         <v>0.53800000000000003</v>
       </c>
     </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>800</v>
       </c>
@@ -1475,7 +1481,7 @@
         <v>0.49199999999999999</v>
       </c>
     </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>900</v>
       </c>
@@ -1525,7 +1531,7 @@
         <v>0.41499999999999998</v>
       </c>
     </row>
-    <row r="30" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>1000</v>
       </c>
@@ -1575,7 +1581,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="31" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>2000</v>
       </c>
@@ -1625,7 +1631,7 @@
         <v>0.76800000000000002</v>
       </c>
     </row>
-    <row r="32" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>3000</v>
       </c>
